--- a/data/nzd0122/nzd0122.xlsx
+++ b/data/nzd0122/nzd0122.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y293"/>
+  <dimension ref="A1:Y296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24168,6 +24168,249 @@
         </is>
       </c>
     </row>
+    <row r="294">
+      <c r="A294" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:02+00:00</t>
+        </is>
+      </c>
+      <c r="B294" t="n">
+        <v>354.62</v>
+      </c>
+      <c r="C294" t="n">
+        <v>338.47</v>
+      </c>
+      <c r="D294" t="n">
+        <v>341.21</v>
+      </c>
+      <c r="E294" t="n">
+        <v>351.89</v>
+      </c>
+      <c r="F294" t="n">
+        <v>357.91</v>
+      </c>
+      <c r="G294" t="n">
+        <v>361.47</v>
+      </c>
+      <c r="H294" t="n">
+        <v>354.12</v>
+      </c>
+      <c r="I294" t="n">
+        <v>348.72</v>
+      </c>
+      <c r="J294" t="n">
+        <v>357.88</v>
+      </c>
+      <c r="K294" t="n">
+        <v>400.67</v>
+      </c>
+      <c r="L294" t="n">
+        <v>360.33</v>
+      </c>
+      <c r="M294" t="n">
+        <v>358.56</v>
+      </c>
+      <c r="N294" t="n">
+        <v>358.19</v>
+      </c>
+      <c r="O294" t="n">
+        <v>360.86</v>
+      </c>
+      <c r="P294" t="n">
+        <v>367.9</v>
+      </c>
+      <c r="Q294" t="n">
+        <v>367.82</v>
+      </c>
+      <c r="R294" t="n">
+        <v>361.04</v>
+      </c>
+      <c r="S294" t="n">
+        <v>356.18</v>
+      </c>
+      <c r="T294" t="n">
+        <v>364.81</v>
+      </c>
+      <c r="U294" t="n">
+        <v>374.68</v>
+      </c>
+      <c r="V294" t="n">
+        <v>380.72</v>
+      </c>
+      <c r="W294" t="n">
+        <v>369.91</v>
+      </c>
+      <c r="X294" t="n">
+        <v>371.73</v>
+      </c>
+      <c r="Y294" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B295" t="n">
+        <v>355.41</v>
+      </c>
+      <c r="C295" t="n">
+        <v>339.64</v>
+      </c>
+      <c r="D295" t="n">
+        <v>341.81</v>
+      </c>
+      <c r="E295" t="n">
+        <v>351.7</v>
+      </c>
+      <c r="F295" t="n">
+        <v>358.19</v>
+      </c>
+      <c r="G295" t="n">
+        <v>361.11</v>
+      </c>
+      <c r="H295" t="n">
+        <v>354.08</v>
+      </c>
+      <c r="I295" t="n">
+        <v>348.74</v>
+      </c>
+      <c r="J295" t="n">
+        <v>357.92</v>
+      </c>
+      <c r="K295" t="n">
+        <v>403.16</v>
+      </c>
+      <c r="L295" t="n">
+        <v>361.15</v>
+      </c>
+      <c r="M295" t="n">
+        <v>359.67</v>
+      </c>
+      <c r="N295" t="n">
+        <v>359</v>
+      </c>
+      <c r="O295" t="n">
+        <v>361.51</v>
+      </c>
+      <c r="P295" t="n">
+        <v>368.68</v>
+      </c>
+      <c r="Q295" t="n">
+        <v>368.83</v>
+      </c>
+      <c r="R295" t="n">
+        <v>362.06</v>
+      </c>
+      <c r="S295" t="n">
+        <v>357.46</v>
+      </c>
+      <c r="T295" t="n">
+        <v>365.77</v>
+      </c>
+      <c r="U295" t="n">
+        <v>374.41</v>
+      </c>
+      <c r="V295" t="n">
+        <v>380.76</v>
+      </c>
+      <c r="W295" t="n">
+        <v>370.56</v>
+      </c>
+      <c r="X295" t="n">
+        <v>372.47</v>
+      </c>
+      <c r="Y295" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B296" t="n">
+        <v>355.17</v>
+      </c>
+      <c r="C296" t="n">
+        <v>340.36</v>
+      </c>
+      <c r="D296" t="n">
+        <v>341.81</v>
+      </c>
+      <c r="E296" t="n">
+        <v>350.95</v>
+      </c>
+      <c r="F296" t="n">
+        <v>358.45</v>
+      </c>
+      <c r="G296" t="n">
+        <v>360.19</v>
+      </c>
+      <c r="H296" t="n">
+        <v>352.91</v>
+      </c>
+      <c r="I296" t="n">
+        <v>347.13</v>
+      </c>
+      <c r="J296" t="n">
+        <v>356.4</v>
+      </c>
+      <c r="K296" t="n">
+        <v>404.16</v>
+      </c>
+      <c r="L296" t="n">
+        <v>360.29</v>
+      </c>
+      <c r="M296" t="n">
+        <v>359.22</v>
+      </c>
+      <c r="N296" t="n">
+        <v>357.64</v>
+      </c>
+      <c r="O296" t="n">
+        <v>360.02</v>
+      </c>
+      <c r="P296" t="n">
+        <v>366.95</v>
+      </c>
+      <c r="Q296" t="n">
+        <v>367.42</v>
+      </c>
+      <c r="R296" t="n">
+        <v>361.85</v>
+      </c>
+      <c r="S296" t="n">
+        <v>357.06</v>
+      </c>
+      <c r="T296" t="n">
+        <v>365.1</v>
+      </c>
+      <c r="U296" t="n">
+        <v>374.22</v>
+      </c>
+      <c r="V296" t="n">
+        <v>379.95</v>
+      </c>
+      <c r="W296" t="n">
+        <v>370</v>
+      </c>
+      <c r="X296" t="n">
+        <v>371.16</v>
+      </c>
+      <c r="Y296" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24179,7 +24422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B299"/>
+  <dimension ref="A1:B302"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27172,6 +27415,36 @@
       </c>
       <c r="B299" t="n">
         <v>-0.7</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B300" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B301" t="n">
+        <v>-0.87</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B302" t="n">
+        <v>-0.3</v>
       </c>
     </row>
   </sheetData>
@@ -27340,28 +27613,28 @@
         <v>0.1526</v>
       </c>
       <c r="I2" t="n">
-        <v>0.210926096282721</v>
+        <v>0.2032840037025129</v>
       </c>
       <c r="J2" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="K2" t="n">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="L2" t="n">
-        <v>0.06146947094366428</v>
+        <v>0.05834549721248983</v>
       </c>
       <c r="M2" t="n">
-        <v>4.621454536409171</v>
+        <v>4.605090656080807</v>
       </c>
       <c r="N2" t="n">
-        <v>34.97380056864214</v>
+        <v>34.75203610327114</v>
       </c>
       <c r="O2" t="n">
-        <v>5.913865112482879</v>
+        <v>5.89508575877155</v>
       </c>
       <c r="P2" t="n">
-        <v>353.0661716700319</v>
+        <v>353.154154910446</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -27418,28 +27691,28 @@
         <v>0.1234</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1522979618491534</v>
+        <v>0.1341718587997139</v>
       </c>
       <c r="J3" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="K3" t="n">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03583855122816437</v>
+        <v>0.02799730695214286</v>
       </c>
       <c r="M3" t="n">
-        <v>4.766578608409634</v>
+        <v>4.793220796701403</v>
       </c>
       <c r="N3" t="n">
-        <v>32.12778394451127</v>
+        <v>32.56594489451923</v>
       </c>
       <c r="O3" t="n">
-        <v>5.668137608113557</v>
+        <v>5.706657944411881</v>
       </c>
       <c r="P3" t="n">
-        <v>344.1433509429634</v>
+        <v>344.352027602808</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27496,28 +27769,28 @@
         <v>0.1286</v>
       </c>
       <c r="I4" t="n">
-        <v>0.109787352329209</v>
+        <v>0.09589480653528956</v>
       </c>
       <c r="J4" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="K4" t="n">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01143893447333322</v>
+        <v>0.008871881132877957</v>
       </c>
       <c r="M4" t="n">
-        <v>6.014152360296502</v>
+        <v>6.006724467442052</v>
       </c>
       <c r="N4" t="n">
-        <v>53.63099113395544</v>
+        <v>53.52958284974894</v>
       </c>
       <c r="O4" t="n">
-        <v>7.323318314395151</v>
+        <v>7.316391381668216</v>
       </c>
       <c r="P4" t="n">
-        <v>345.3632228550092</v>
+        <v>345.5231699990204</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27574,28 +27847,28 @@
         <v>0.1132</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1127052693701656</v>
+        <v>0.1034589655606243</v>
       </c>
       <c r="J5" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="K5" t="n">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0110710927535036</v>
+        <v>0.009521122369851254</v>
       </c>
       <c r="M5" t="n">
-        <v>6.200587046430105</v>
+        <v>6.173378607467162</v>
       </c>
       <c r="N5" t="n">
-        <v>58.41929283013575</v>
+        <v>58.02069629294963</v>
       </c>
       <c r="O5" t="n">
-        <v>7.643251456686202</v>
+        <v>7.617131762871746</v>
       </c>
       <c r="P5" t="n">
-        <v>352.9416097342328</v>
+        <v>353.0480784123877</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27652,28 +27925,28 @@
         <v>0.1246</v>
       </c>
       <c r="I6" t="n">
-        <v>0.135683430624074</v>
+        <v>0.1193663437611107</v>
       </c>
       <c r="J6" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="K6" t="n">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01466175360505551</v>
+        <v>0.01152689215559055</v>
       </c>
       <c r="M6" t="n">
-        <v>6.384065688756358</v>
+        <v>6.385261540943138</v>
       </c>
       <c r="N6" t="n">
-        <v>63.70101105899884</v>
+        <v>63.66577245581616</v>
       </c>
       <c r="O6" t="n">
-        <v>7.981291315257128</v>
+        <v>7.979083434569171</v>
       </c>
       <c r="P6" t="n">
-        <v>362.4069004361284</v>
+        <v>362.5947626330442</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -27730,28 +28003,28 @@
         <v>0.1069</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1257540406972184</v>
+        <v>0.1103438319332341</v>
       </c>
       <c r="J7" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="K7" t="n">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01496868163279708</v>
+        <v>0.01170140423865407</v>
       </c>
       <c r="M7" t="n">
-        <v>5.804479149096431</v>
+        <v>5.811212264249653</v>
       </c>
       <c r="N7" t="n">
-        <v>53.58011664396848</v>
+        <v>53.58409747199435</v>
       </c>
       <c r="O7" t="n">
-        <v>7.319844031396331</v>
+        <v>7.320115946622318</v>
       </c>
       <c r="P7" t="n">
-        <v>364.9750529923946</v>
+        <v>365.1524937651429</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -27808,28 +28081,28 @@
         <v>0.1028</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1344621717215179</v>
+        <v>0.1259353260023573</v>
       </c>
       <c r="J8" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="K8" t="n">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01760666336656824</v>
+        <v>0.01576947646914173</v>
       </c>
       <c r="M8" t="n">
-        <v>5.975054776418557</v>
+        <v>5.94802306695562</v>
       </c>
       <c r="N8" t="n">
-        <v>51.92674549169125</v>
+        <v>51.56812738640222</v>
       </c>
       <c r="O8" t="n">
-        <v>7.206021474551075</v>
+        <v>7.181095138375638</v>
       </c>
       <c r="P8" t="n">
-        <v>354.1963770815614</v>
+        <v>354.294465609131</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -27886,28 +28159,28 @@
         <v>0.103</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1335272618691035</v>
+        <v>0.1236195580787648</v>
       </c>
       <c r="J9" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="K9" t="n">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01560066619584166</v>
+        <v>0.01364456974143058</v>
       </c>
       <c r="M9" t="n">
-        <v>6.235765136971155</v>
+        <v>6.211953568954979</v>
       </c>
       <c r="N9" t="n">
-        <v>57.90960031258901</v>
+        <v>57.55123309412358</v>
       </c>
       <c r="O9" t="n">
-        <v>7.609835761209897</v>
+        <v>7.586252902067238</v>
       </c>
       <c r="P9" t="n">
-        <v>349.3824291614551</v>
+        <v>349.4964045272388</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -27964,28 +28237,28 @@
         <v>0.1145</v>
       </c>
       <c r="I10" t="n">
-        <v>0.03745499552239245</v>
+        <v>0.03720282634529429</v>
       </c>
       <c r="J10" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="K10" t="n">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="L10" t="n">
-        <v>0.00153895577986829</v>
+        <v>0.001552322627312197</v>
       </c>
       <c r="M10" t="n">
-        <v>5.382639676208637</v>
+        <v>5.334107572679628</v>
       </c>
       <c r="N10" t="n">
-        <v>46.8497197293774</v>
+        <v>46.3769152797938</v>
       </c>
       <c r="O10" t="n">
-        <v>6.844685509895791</v>
+        <v>6.810059858752624</v>
       </c>
       <c r="P10" t="n">
-        <v>356.5107002132805</v>
+        <v>356.5136181123757</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -28042,28 +28315,28 @@
         <v>0.0873</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3301550334064428</v>
+        <v>0.3113094089232825</v>
       </c>
       <c r="J11" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="K11" t="n">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="L11" t="n">
-        <v>0.06491931556708264</v>
+        <v>0.05878471245730099</v>
       </c>
       <c r="M11" t="n">
-        <v>7.057444360248395</v>
+        <v>7.081076743522369</v>
       </c>
       <c r="N11" t="n">
-        <v>80.90302124774666</v>
+        <v>80.92024284782103</v>
       </c>
       <c r="O11" t="n">
-        <v>8.994610677941912</v>
+        <v>8.995567955822525</v>
       </c>
       <c r="P11" t="n">
-        <v>402.8714765535004</v>
+        <v>403.0883118320842</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -28120,28 +28393,28 @@
         <v>0.1136</v>
       </c>
       <c r="I12" t="n">
-        <v>0.06212074641326281</v>
+        <v>0.05133940173620036</v>
       </c>
       <c r="J12" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="K12" t="n">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="L12" t="n">
-        <v>0.005664692335037302</v>
+        <v>0.003932337093285221</v>
       </c>
       <c r="M12" t="n">
-        <v>4.786919369756144</v>
+        <v>4.778649233464423</v>
       </c>
       <c r="N12" t="n">
-        <v>34.86682312371788</v>
+        <v>34.78134510219028</v>
       </c>
       <c r="O12" t="n">
-        <v>5.904813555373098</v>
+        <v>5.897571118875149</v>
       </c>
       <c r="P12" t="n">
-        <v>364.1283670084121</v>
+        <v>364.2523745117777</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -28198,28 +28471,28 @@
         <v>0.0838</v>
       </c>
       <c r="I13" t="n">
-        <v>0.08661819922822406</v>
+        <v>0.06874848940588829</v>
       </c>
       <c r="J13" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="K13" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="L13" t="n">
-        <v>0.00832359519567305</v>
+        <v>0.005290596062393016</v>
       </c>
       <c r="M13" t="n">
-        <v>5.745542569698295</v>
+        <v>5.755221780259361</v>
       </c>
       <c r="N13" t="n">
-        <v>46.66672747437894</v>
+        <v>46.9482788938158</v>
       </c>
       <c r="O13" t="n">
-        <v>6.831304961307096</v>
+        <v>6.851881412708177</v>
       </c>
       <c r="P13" t="n">
-        <v>365.5626989893497</v>
+        <v>365.7664555039244</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -28276,28 +28549,28 @@
         <v>0.0814</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1160365134944541</v>
+        <v>0.09962377563785063</v>
       </c>
       <c r="J14" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="K14" t="n">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01514913357735248</v>
+        <v>0.01130429202769478</v>
       </c>
       <c r="M14" t="n">
-        <v>5.539459844628297</v>
+        <v>5.550088785193618</v>
       </c>
       <c r="N14" t="n">
-        <v>45.05619708729145</v>
+        <v>45.22222641421496</v>
       </c>
       <c r="O14" t="n">
-        <v>6.712391309160354</v>
+        <v>6.724747312294713</v>
       </c>
       <c r="P14" t="n">
-        <v>363.0833645073772</v>
+        <v>363.2721492943103</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -28354,28 +28627,28 @@
         <v>0.09660000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.05506579841584373</v>
+        <v>0.04194671060620704</v>
       </c>
       <c r="J15" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="K15" t="n">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="L15" t="n">
-        <v>0.00343956898056863</v>
+        <v>0.002025589254262106</v>
       </c>
       <c r="M15" t="n">
-        <v>5.624283777706234</v>
+        <v>5.61542219396512</v>
       </c>
       <c r="N15" t="n">
-        <v>45.2216090189008</v>
+        <v>45.16172337282414</v>
       </c>
       <c r="O15" t="n">
-        <v>6.724701407415856</v>
+        <v>6.720247270214403</v>
       </c>
       <c r="P15" t="n">
-        <v>365.6591001253423</v>
+        <v>365.8100049686188</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -28432,28 +28705,28 @@
         <v>0.0959</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1300248470977682</v>
+        <v>0.1170567868065961</v>
       </c>
       <c r="J16" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="K16" t="n">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="L16" t="n">
-        <v>0.01727757785518835</v>
+        <v>0.01424828412921519</v>
       </c>
       <c r="M16" t="n">
-        <v>5.944006977592124</v>
+        <v>5.932769979901853</v>
       </c>
       <c r="N16" t="n">
-        <v>49.49749541224675</v>
+        <v>49.38611205088726</v>
       </c>
       <c r="O16" t="n">
-        <v>7.035445644182517</v>
+        <v>7.027525314852111</v>
       </c>
       <c r="P16" t="n">
-        <v>370.6058433664725</v>
+        <v>370.7550126827445</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -28510,28 +28783,28 @@
         <v>0.0883</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2432710270615255</v>
+        <v>0.2204473106286092</v>
       </c>
       <c r="J17" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="K17" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="L17" t="n">
-        <v>0.05844221726519661</v>
+        <v>0.04837782770145049</v>
       </c>
       <c r="M17" t="n">
-        <v>5.935231966947557</v>
+        <v>5.968534589511031</v>
       </c>
       <c r="N17" t="n">
-        <v>49.77727143034193</v>
+        <v>50.50443713639589</v>
       </c>
       <c r="O17" t="n">
-        <v>7.055300945412742</v>
+        <v>7.106647390745927</v>
       </c>
       <c r="P17" t="n">
-        <v>372.6339127596265</v>
+        <v>372.8941701700188</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -28588,28 +28861,28 @@
         <v>0.0919</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1986267184490666</v>
+        <v>0.1825796283545974</v>
       </c>
       <c r="J18" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="K18" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="L18" t="n">
-        <v>0.04181067133186811</v>
+        <v>0.03587370927740419</v>
       </c>
       <c r="M18" t="n">
-        <v>5.789807510300943</v>
+        <v>5.796921933835435</v>
       </c>
       <c r="N18" t="n">
-        <v>47.2029934092153</v>
+        <v>47.33299828130048</v>
       </c>
       <c r="O18" t="n">
-        <v>6.870443465251373</v>
+        <v>6.879898130154289</v>
       </c>
       <c r="P18" t="n">
-        <v>364.1474631547536</v>
+        <v>364.3304351808648</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -28666,28 +28939,28 @@
         <v>0.1224</v>
       </c>
       <c r="I19" t="n">
-        <v>0.2003535543324496</v>
+        <v>0.182316188465841</v>
       </c>
       <c r="J19" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="K19" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="L19" t="n">
-        <v>0.04427454936383146</v>
+        <v>0.03712302673284751</v>
       </c>
       <c r="M19" t="n">
-        <v>5.660198728486908</v>
+        <v>5.672540885411515</v>
       </c>
       <c r="N19" t="n">
-        <v>45.23797131308713</v>
+        <v>45.54908161912865</v>
       </c>
       <c r="O19" t="n">
-        <v>6.725917878853943</v>
+        <v>6.749005972669505</v>
       </c>
       <c r="P19" t="n">
-        <v>360.3261010999391</v>
+        <v>360.5317671589279</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -28744,28 +29017,28 @@
         <v>0.1034</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2082726886961406</v>
+        <v>0.1956039691030688</v>
       </c>
       <c r="J20" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="K20" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="L20" t="n">
-        <v>0.05089952111138363</v>
+        <v>0.04573367499194025</v>
       </c>
       <c r="M20" t="n">
-        <v>5.470361148625577</v>
+        <v>5.458456675389725</v>
       </c>
       <c r="N20" t="n">
-        <v>42.22728504239055</v>
+        <v>42.17844454536977</v>
       </c>
       <c r="O20" t="n">
-        <v>6.498252460653599</v>
+        <v>6.494493401749653</v>
       </c>
       <c r="P20" t="n">
-        <v>365.8118576463022</v>
+        <v>365.9563132752721</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -28822,28 +29095,28 @@
         <v>0.0847</v>
       </c>
       <c r="I21" t="n">
-        <v>0.09991534539315888</v>
+        <v>0.08704303084681728</v>
       </c>
       <c r="J21" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="K21" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="L21" t="n">
-        <v>0.01059253951454864</v>
+        <v>0.008172613004906126</v>
       </c>
       <c r="M21" t="n">
-        <v>5.788051652902382</v>
+        <v>5.767664840262339</v>
       </c>
       <c r="N21" t="n">
-        <v>48.68212110811987</v>
+        <v>48.57859029604669</v>
       </c>
       <c r="O21" t="n">
-        <v>6.977257420227512</v>
+        <v>6.969834309081292</v>
       </c>
       <c r="P21" t="n">
-        <v>378.0440545016766</v>
+        <v>378.1908374501887</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -28900,28 +29173,28 @@
         <v>0.0767</v>
       </c>
       <c r="I22" t="n">
-        <v>0.02436461688041555</v>
+        <v>0.01463744995256118</v>
       </c>
       <c r="J22" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="K22" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0007501603550508218</v>
+        <v>0.0002754233636386161</v>
       </c>
       <c r="M22" t="n">
-        <v>5.308842720662547</v>
+        <v>5.290021859050445</v>
       </c>
       <c r="N22" t="n">
-        <v>41.2828021861683</v>
+        <v>41.08773241167998</v>
       </c>
       <c r="O22" t="n">
-        <v>6.425169428596284</v>
+        <v>6.409971326899987</v>
       </c>
       <c r="P22" t="n">
-        <v>384.5809367227722</v>
+        <v>384.6918610882262</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -28978,28 +29251,28 @@
         <v>0.0697</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.02413856325974109</v>
+        <v>-0.04016641579910391</v>
       </c>
       <c r="J23" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="K23" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0007858201869550552</v>
+        <v>0.002186715958077956</v>
       </c>
       <c r="M23" t="n">
-        <v>5.169856638491578</v>
+        <v>5.189557052758834</v>
       </c>
       <c r="N23" t="n">
-        <v>38.68015964088714</v>
+        <v>38.89419641984455</v>
       </c>
       <c r="O23" t="n">
-        <v>6.219337556435343</v>
+        <v>6.236521179298965</v>
       </c>
       <c r="P23" t="n">
-        <v>378.6573434670206</v>
+        <v>378.8401034927127</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -29056,28 +29329,28 @@
         <v>0.06610000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1018739598185219</v>
+        <v>-0.1259334661564122</v>
       </c>
       <c r="J24" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="K24" t="n">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="L24" t="n">
-        <v>0.009425761368382579</v>
+        <v>0.01430580578485185</v>
       </c>
       <c r="M24" t="n">
-        <v>6.219604963990507</v>
+        <v>6.263421825832775</v>
       </c>
       <c r="N24" t="n">
-        <v>56.94124780643082</v>
+        <v>57.73164389607857</v>
       </c>
       <c r="O24" t="n">
-        <v>7.545942473040118</v>
+        <v>7.598134237829611</v>
       </c>
       <c r="P24" t="n">
-        <v>386.3199786619303</v>
+        <v>386.5943283601321</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -29115,7 +29388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y293"/>
+  <dimension ref="A1:Y296"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66245,6 +66518,387 @@
         </is>
       </c>
     </row>
+    <row r="294">
+      <c r="A294" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:05:02+00:00</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>-36.26035865038945,175.4897770951085</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>-36.26108946558603,175.48993055577662</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>-36.26175702854449,175.49027912359588</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>-36.26239800084406,175.49070970251887</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>-36.263056842024305,175.4910929863943</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>-36.263659049690695,175.49156839111396</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>-36.26423737130433,175.49211720425745</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>-36.26480365390493,175.49268226281296</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>-36.265279526748905,175.49336470431288</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>-36.265546577597064,175.49431827139733</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>-36.26633031567987,175.4946019564691</t>
+        </is>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>-36.26678947413234,175.4952904738303</t>
+        </is>
+      </c>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>-36.26717948386873,175.49604923570965</t>
+        </is>
+      </c>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>-36.26754533207894,175.4968244729661</t>
+        </is>
+      </c>
+      <c r="P294" t="inlineStr">
+        <is>
+          <t>-36.26787635434382,175.49762213301057</t>
+        </is>
+      </c>
+      <c r="Q294" t="inlineStr">
+        <is>
+          <t>-36.26820413841259,175.4984000831597</t>
+        </is>
+      </c>
+      <c r="R294" t="inlineStr">
+        <is>
+          <t>-36.268441566216396,175.49924431802324</t>
+        </is>
+      </c>
+      <c r="S294" t="inlineStr">
+        <is>
+          <t>-36.26866365584918,175.50010206759762</t>
+        </is>
+      </c>
+      <c r="T294" t="inlineStr">
+        <is>
+          <t>-36.268767513401926,175.50099461905663</t>
+        </is>
+      </c>
+      <c r="U294" t="inlineStr">
+        <is>
+          <t>-36.268859635754474,175.50188402211035</t>
+        </is>
+      </c>
+      <c r="V294" t="inlineStr">
+        <is>
+          <t>-36.268922773056545,175.50273943911162</t>
+        </is>
+      </c>
+      <c r="W294" t="inlineStr">
+        <is>
+          <t>-36.26897514755016,175.5036203836549</t>
+        </is>
+      </c>
+      <c r="X294" t="inlineStr">
+        <is>
+          <t>-36.26891266870367,175.50451523842034</t>
+        </is>
+      </c>
+      <c r="Y294" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:05:11+00:00</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>-36.26035600535657,175.48978525467356</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>-36.26108554825163,175.48994264030352</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>-36.26175501964186,175.49028532083418</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>-36.26239863700202,175.4907077400472</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>-36.26305572387157,175.49109577887103</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>-36.263661014316085,175.49156520414982</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>-36.264237619671526,175.4921168817779</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>-36.264803529720865,175.49268242405327</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>-36.26527927837955,175.49336502679378</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>-36.26553111648546,175.49433834574077</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>-36.266324819251764,175.4946080530198</t>
+        </is>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>-36.26678121631806,175.49529744067453</t>
+        </is>
+      </c>
+      <c r="N295" t="inlineStr">
+        <is>
+          <t>-36.26717324933827,175.49605392048585</t>
+        </is>
+      </c>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>-36.2675403290463,175.4968282323369</t>
+        </is>
+      </c>
+      <c r="P295" t="inlineStr">
+        <is>
+          <t>-36.26787020363719,175.49762633129527</t>
+        </is>
+      </c>
+      <c r="Q295" t="inlineStr">
+        <is>
+          <t>-36.268195583495896,175.49840391414804</t>
+        </is>
+      </c>
+      <c r="R295" t="inlineStr">
+        <is>
+          <t>-36.26843262654594,175.49924694952492</t>
+        </is>
+      </c>
+      <c r="S295" t="inlineStr">
+        <is>
+          <t>-36.26865243742872,175.50010536980125</t>
+        </is>
+      </c>
+      <c r="T295" t="inlineStr">
+        <is>
+          <t>-36.26875909957819,175.50099709564796</t>
+        </is>
+      </c>
+      <c r="U295" t="inlineStr">
+        <is>
+          <t>-36.26886202372284,175.50188344878822</t>
+        </is>
+      </c>
+      <c r="V295" t="inlineStr">
+        <is>
+          <t>-36.26892241286692,175.5027394542068</t>
+        </is>
+      </c>
+      <c r="W295" t="inlineStr">
+        <is>
+          <t>-36.26896931015082,175.50361980081377</t>
+        </is>
+      </c>
+      <c r="X295" t="inlineStr">
+        <is>
+          <t>-36.268906023055145,175.50451457482987</t>
+        </is>
+      </c>
+      <c r="Y295" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:05:24+00:00</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>-36.26035680891092,175.48978277581844</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>-36.26108313758374,175.48995007693483</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>-36.26175501964186,175.49028532083418</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>-36.26240114815156,175.49069999344817</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>-36.26305468558682,175.49109837188504</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>-36.26366603502503,175.4915570596853</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>-36.264244884411355,175.49210744924915</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>-36.2648135265371,175.4926694442067</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>-36.26528871641419,175.49335277251782</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>-36.265524907202824,175.49434640772384</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>-36.2663305837983,175.49460165907638</t>
+        </is>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>-36.26678456408066,175.4952946162784</t>
+        </is>
+      </c>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>-36.26718371719179,175.4960460546884</t>
+        </is>
+      </c>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>-36.26755179753635,175.49681961470162</t>
+        </is>
+      </c>
+      <c r="P296" t="inlineStr">
+        <is>
+          <t>-36.26788384558891,175.49761701971423</t>
+        </is>
+      </c>
+      <c r="Q296" t="inlineStr">
+        <is>
+          <t>-36.26820752649837,175.49839856593638</t>
+        </is>
+      </c>
+      <c r="R296" t="inlineStr">
+        <is>
+          <t>-36.26843446706633,175.49924640774523</t>
+        </is>
+      </c>
+      <c r="S296" t="inlineStr">
+        <is>
+          <t>-36.26865594318513,175.5001043378627</t>
+        </is>
+      </c>
+      <c r="T296" t="inlineStr">
+        <is>
+          <t>-36.26876497172602,175.50099536719364</t>
+        </is>
+      </c>
+      <c r="U296" t="inlineStr">
+        <is>
+          <t>-36.268863704145026,175.50188304533927</t>
+        </is>
+      </c>
+      <c r="V296" t="inlineStr">
+        <is>
+          <t>-36.268929706707056,175.50273914852946</t>
+        </is>
+      </c>
+      <c r="W296" t="inlineStr">
+        <is>
+          <t>-36.26897433929487,175.5036203029538</t>
+        </is>
+      </c>
+      <c r="X296" t="inlineStr">
+        <is>
+          <t>-36.26891778764915,175.50451574956446</t>
+        </is>
+      </c>
+      <c r="Y296" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0122/nzd0122.xlsx
+++ b/data/nzd0122/nzd0122.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y296"/>
+  <dimension ref="A1:Y297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24411,6 +24411,87 @@
         </is>
       </c>
     </row>
+    <row r="297">
+      <c r="A297" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B297" t="n">
+        <v>355.73</v>
+      </c>
+      <c r="C297" t="n">
+        <v>342.06</v>
+      </c>
+      <c r="D297" t="n">
+        <v>343.64</v>
+      </c>
+      <c r="E297" t="n">
+        <v>352.34</v>
+      </c>
+      <c r="F297" t="n">
+        <v>360.11</v>
+      </c>
+      <c r="G297" t="n">
+        <v>361.01</v>
+      </c>
+      <c r="H297" t="n">
+        <v>354.06</v>
+      </c>
+      <c r="I297" t="n">
+        <v>348.64</v>
+      </c>
+      <c r="J297" t="n">
+        <v>357.51</v>
+      </c>
+      <c r="K297" t="n">
+        <v>404.16</v>
+      </c>
+      <c r="L297" t="n">
+        <v>362.18</v>
+      </c>
+      <c r="M297" t="n">
+        <v>361.67</v>
+      </c>
+      <c r="N297" t="n">
+        <v>359.35</v>
+      </c>
+      <c r="O297" t="n">
+        <v>361.73</v>
+      </c>
+      <c r="P297" t="n">
+        <v>368.4</v>
+      </c>
+      <c r="Q297" t="n">
+        <v>369.42</v>
+      </c>
+      <c r="R297" t="n">
+        <v>363.43</v>
+      </c>
+      <c r="S297" t="n">
+        <v>358.6</v>
+      </c>
+      <c r="T297" t="n">
+        <v>366.69</v>
+      </c>
+      <c r="U297" t="n">
+        <v>375.7</v>
+      </c>
+      <c r="V297" t="n">
+        <v>380.99</v>
+      </c>
+      <c r="W297" t="n">
+        <v>371.68</v>
+      </c>
+      <c r="X297" t="n">
+        <v>373.14</v>
+      </c>
+      <c r="Y297" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24422,7 +24503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B302"/>
+  <dimension ref="A1:B303"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27445,6 +27526,16 @@
       </c>
       <c r="B302" t="n">
         <v>-0.3</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B303" t="n">
+        <v>0.32</v>
       </c>
     </row>
   </sheetData>
@@ -27613,28 +27704,28 @@
         <v>0.1526</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2032840037025129</v>
+        <v>0.2012791172244049</v>
       </c>
       <c r="J2" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K2" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05834549721248983</v>
+        <v>0.05761573033569178</v>
       </c>
       <c r="M2" t="n">
-        <v>4.605090656080807</v>
+        <v>4.597467509547885</v>
       </c>
       <c r="N2" t="n">
-        <v>34.75203610327114</v>
+        <v>34.66256537174345</v>
       </c>
       <c r="O2" t="n">
-        <v>5.89508575877155</v>
+        <v>5.887492282096296</v>
       </c>
       <c r="P2" t="n">
-        <v>353.154154910446</v>
+        <v>353.1772930330886</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -27691,28 +27782,28 @@
         <v>0.1234</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1341718587997139</v>
+        <v>0.1301103447817787</v>
       </c>
       <c r="J3" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K3" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02799730695214286</v>
+        <v>0.02646622213420124</v>
       </c>
       <c r="M3" t="n">
-        <v>4.793220796701403</v>
+        <v>4.793657782180372</v>
       </c>
       <c r="N3" t="n">
-        <v>32.56594489451923</v>
+        <v>32.57309555709423</v>
       </c>
       <c r="O3" t="n">
-        <v>5.706657944411881</v>
+        <v>5.707284429314369</v>
       </c>
       <c r="P3" t="n">
-        <v>344.352027602808</v>
+        <v>344.3989009846618</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27769,28 +27860,28 @@
         <v>0.1286</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09589480653528956</v>
+        <v>0.09282484298846298</v>
       </c>
       <c r="J4" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K4" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L4" t="n">
-        <v>0.008871881132877957</v>
+        <v>0.00836745263991201</v>
       </c>
       <c r="M4" t="n">
-        <v>6.006724467442052</v>
+        <v>5.998407572566356</v>
       </c>
       <c r="N4" t="n">
-        <v>53.52958284974894</v>
+        <v>53.4148807475086</v>
       </c>
       <c r="O4" t="n">
-        <v>7.316391381668216</v>
+        <v>7.308548470627297</v>
       </c>
       <c r="P4" t="n">
-        <v>345.5231699990204</v>
+        <v>345.5586000315088</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27847,28 +27938,28 @@
         <v>0.1132</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1034589655606243</v>
+        <v>0.1010523720412122</v>
       </c>
       <c r="J5" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K5" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L5" t="n">
-        <v>0.009521122369851254</v>
+        <v>0.009146703926998567</v>
       </c>
       <c r="M5" t="n">
-        <v>6.173378607467162</v>
+        <v>6.161806085336472</v>
       </c>
       <c r="N5" t="n">
-        <v>58.02069629294963</v>
+        <v>57.864748291048</v>
       </c>
       <c r="O5" t="n">
-        <v>7.617131762871746</v>
+        <v>7.606888213392385</v>
       </c>
       <c r="P5" t="n">
-        <v>353.0480784123877</v>
+        <v>353.0758525814548</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -27925,28 +28016,28 @@
         <v>0.1246</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1193663437611107</v>
+        <v>0.115446125831547</v>
       </c>
       <c r="J6" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K6" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01152689215559055</v>
+        <v>0.01084974921391113</v>
       </c>
       <c r="M6" t="n">
-        <v>6.385261540943138</v>
+        <v>6.379454916693716</v>
       </c>
       <c r="N6" t="n">
-        <v>63.66577245581616</v>
+        <v>63.55907952135894</v>
       </c>
       <c r="O6" t="n">
-        <v>7.979083434569171</v>
+        <v>7.972394842289169</v>
       </c>
       <c r="P6" t="n">
-        <v>362.5947626330442</v>
+        <v>362.6400053359256</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28003,28 +28094,28 @@
         <v>0.1069</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1103438319332341</v>
+        <v>0.1054524199561186</v>
       </c>
       <c r="J7" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K7" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01170140423865407</v>
+        <v>0.01074123938623472</v>
       </c>
       <c r="M7" t="n">
-        <v>5.811212264249653</v>
+        <v>5.812891013406333</v>
       </c>
       <c r="N7" t="n">
-        <v>53.58409747199435</v>
+        <v>53.57287050242482</v>
       </c>
       <c r="O7" t="n">
-        <v>7.320115946622318</v>
+        <v>7.319349049090692</v>
       </c>
       <c r="P7" t="n">
-        <v>365.1524937651429</v>
+        <v>365.2089448866692</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28081,28 +28172,28 @@
         <v>0.1028</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1259353260023573</v>
+        <v>0.1234420504843355</v>
       </c>
       <c r="J8" t="n">
+        <v>296</v>
+      </c>
+      <c r="K8" t="n">
         <v>295</v>
       </c>
-      <c r="K8" t="n">
-        <v>294</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.01576947646914173</v>
+        <v>0.01525703621230035</v>
       </c>
       <c r="M8" t="n">
-        <v>5.94802306695562</v>
+        <v>5.937912320047518</v>
       </c>
       <c r="N8" t="n">
-        <v>51.56812738640222</v>
+        <v>51.43769217879193</v>
       </c>
       <c r="O8" t="n">
-        <v>7.181095138375638</v>
+        <v>7.17200754174115</v>
       </c>
       <c r="P8" t="n">
-        <v>354.294465609131</v>
+        <v>354.3232105555913</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -28159,28 +28250,28 @@
         <v>0.103</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1236195580787648</v>
+        <v>0.1207391676244684</v>
       </c>
       <c r="J9" t="n">
+        <v>296</v>
+      </c>
+      <c r="K9" t="n">
         <v>295</v>
       </c>
-      <c r="K9" t="n">
-        <v>294</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.01364456974143058</v>
+        <v>0.01310513887191045</v>
       </c>
       <c r="M9" t="n">
-        <v>6.211953568954979</v>
+        <v>6.202461749368298</v>
       </c>
       <c r="N9" t="n">
-        <v>57.55123309412358</v>
+        <v>57.41536455289468</v>
       </c>
       <c r="O9" t="n">
-        <v>7.586252902067238</v>
+        <v>7.577292692835264</v>
       </c>
       <c r="P9" t="n">
-        <v>349.4964045272388</v>
+        <v>349.5296125176093</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -28237,28 +28328,28 @@
         <v>0.1145</v>
       </c>
       <c r="I10" t="n">
-        <v>0.03720282634529429</v>
+        <v>0.03719326192148134</v>
       </c>
       <c r="J10" t="n">
+        <v>296</v>
+      </c>
+      <c r="K10" t="n">
         <v>295</v>
       </c>
-      <c r="K10" t="n">
-        <v>294</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.001552322627312197</v>
+        <v>0.00156287624424345</v>
       </c>
       <c r="M10" t="n">
-        <v>5.334107572679628</v>
+        <v>5.316072485564702</v>
       </c>
       <c r="N10" t="n">
-        <v>46.3769152797938</v>
+        <v>46.21970605044874</v>
       </c>
       <c r="O10" t="n">
-        <v>6.810059858752624</v>
+        <v>6.798507634065636</v>
       </c>
       <c r="P10" t="n">
-        <v>356.5136181123757</v>
+        <v>356.5137283805143</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -28315,28 +28406,28 @@
         <v>0.0873</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3113094089232825</v>
+        <v>0.306272501298106</v>
       </c>
       <c r="J11" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K11" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="L11" t="n">
-        <v>0.05878471245730099</v>
+        <v>0.05727699849830825</v>
       </c>
       <c r="M11" t="n">
-        <v>7.081076743522369</v>
+        <v>7.082993746485276</v>
       </c>
       <c r="N11" t="n">
-        <v>80.92024284782103</v>
+        <v>80.8265484277688</v>
       </c>
       <c r="O11" t="n">
-        <v>8.995567955822525</v>
+        <v>8.990358637327478</v>
       </c>
       <c r="P11" t="n">
-        <v>403.0883118320842</v>
+        <v>403.1464127653821</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -28393,28 +28484,28 @@
         <v>0.1136</v>
       </c>
       <c r="I12" t="n">
-        <v>0.05133940173620036</v>
+        <v>0.04896695358192362</v>
       </c>
       <c r="J12" t="n">
+        <v>296</v>
+      </c>
+      <c r="K12" t="n">
         <v>295</v>
       </c>
-      <c r="K12" t="n">
-        <v>294</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.003932337093285221</v>
+        <v>0.003600538139880483</v>
       </c>
       <c r="M12" t="n">
-        <v>4.778649233464423</v>
+        <v>4.771563162132486</v>
       </c>
       <c r="N12" t="n">
-        <v>34.78134510219028</v>
+        <v>34.70361779917722</v>
       </c>
       <c r="O12" t="n">
-        <v>5.897571118875149</v>
+        <v>5.890977660726377</v>
       </c>
       <c r="P12" t="n">
-        <v>364.2523745117777</v>
+        <v>364.2797264408692</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -28471,28 +28562,28 @@
         <v>0.0838</v>
       </c>
       <c r="I13" t="n">
-        <v>0.06874848940588829</v>
+        <v>0.06471301620223346</v>
       </c>
       <c r="J13" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K13" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L13" t="n">
-        <v>0.005290596062393016</v>
+        <v>0.004712617099758787</v>
       </c>
       <c r="M13" t="n">
-        <v>5.755221780259361</v>
+        <v>5.751273081306058</v>
       </c>
       <c r="N13" t="n">
-        <v>46.9482788938158</v>
+        <v>46.90836998533674</v>
       </c>
       <c r="O13" t="n">
-        <v>6.851881412708177</v>
+        <v>6.848968534409889</v>
       </c>
       <c r="P13" t="n">
-        <v>365.7664555039244</v>
+        <v>365.8125805095665</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -28549,28 +28640,28 @@
         <v>0.0814</v>
       </c>
       <c r="I14" t="n">
-        <v>0.09962377563785063</v>
+        <v>0.09508873101055224</v>
       </c>
       <c r="J14" t="n">
+        <v>296</v>
+      </c>
+      <c r="K14" t="n">
         <v>295</v>
       </c>
-      <c r="K14" t="n">
-        <v>294</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.01130429202769478</v>
+        <v>0.01035029062092463</v>
       </c>
       <c r="M14" t="n">
-        <v>5.550088785193618</v>
+        <v>5.550141353935225</v>
       </c>
       <c r="N14" t="n">
-        <v>45.22222641421496</v>
+        <v>45.21573261476813</v>
       </c>
       <c r="O14" t="n">
-        <v>6.724747312294713</v>
+        <v>6.724264466450448</v>
       </c>
       <c r="P14" t="n">
-        <v>363.2721492943103</v>
+        <v>363.3244337747316</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -28627,28 +28718,28 @@
         <v>0.09660000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.04194671060620704</v>
+        <v>0.03836915247595857</v>
       </c>
       <c r="J15" t="n">
+        <v>296</v>
+      </c>
+      <c r="K15" t="n">
         <v>295</v>
       </c>
-      <c r="K15" t="n">
-        <v>294</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.002025589254262106</v>
+        <v>0.001704314248293648</v>
       </c>
       <c r="M15" t="n">
-        <v>5.61542219396512</v>
+        <v>5.60963651216357</v>
       </c>
       <c r="N15" t="n">
-        <v>45.16172337282414</v>
+        <v>45.09998979891246</v>
       </c>
       <c r="O15" t="n">
-        <v>6.720247270214403</v>
+        <v>6.715652596651532</v>
       </c>
       <c r="P15" t="n">
-        <v>365.8100049686188</v>
+        <v>365.8512505975793</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -28705,28 +28796,28 @@
         <v>0.0959</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1170567868065961</v>
+        <v>0.113272714540509</v>
       </c>
       <c r="J16" t="n">
+        <v>296</v>
+      </c>
+      <c r="K16" t="n">
         <v>295</v>
       </c>
-      <c r="K16" t="n">
-        <v>294</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.01424828412921519</v>
+        <v>0.01342310498478394</v>
       </c>
       <c r="M16" t="n">
-        <v>5.932769979901853</v>
+        <v>5.927478526576269</v>
       </c>
       <c r="N16" t="n">
-        <v>49.38611205088726</v>
+        <v>49.32091007821322</v>
       </c>
       <c r="O16" t="n">
-        <v>7.027525314852111</v>
+        <v>7.022884740490421</v>
       </c>
       <c r="P16" t="n">
-        <v>370.7550126827445</v>
+        <v>370.7986392109418</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -28783,28 +28874,28 @@
         <v>0.0883</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2204473106286092</v>
+        <v>0.214055878418695</v>
       </c>
       <c r="J17" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K17" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L17" t="n">
-        <v>0.04837782770145049</v>
+        <v>0.04579875039821402</v>
       </c>
       <c r="M17" t="n">
-        <v>5.968534589511031</v>
+        <v>5.974562904177546</v>
       </c>
       <c r="N17" t="n">
-        <v>50.50443713639589</v>
+        <v>50.63156877271932</v>
       </c>
       <c r="O17" t="n">
-        <v>7.106647390745927</v>
+        <v>7.115586326699952</v>
       </c>
       <c r="P17" t="n">
-        <v>372.8941701700188</v>
+        <v>372.9672235225914</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -28861,28 +28952,28 @@
         <v>0.0919</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1825796283545974</v>
+        <v>0.1786253453655476</v>
       </c>
       <c r="J18" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K18" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L18" t="n">
-        <v>0.03587370927740419</v>
+        <v>0.03455048276633432</v>
       </c>
       <c r="M18" t="n">
-        <v>5.796921933835435</v>
+        <v>5.793461454326768</v>
       </c>
       <c r="N18" t="n">
-        <v>47.33299828130048</v>
+        <v>47.28706140509722</v>
       </c>
       <c r="O18" t="n">
-        <v>6.879898130154289</v>
+        <v>6.876558834555058</v>
       </c>
       <c r="P18" t="n">
-        <v>364.3304351808648</v>
+        <v>364.3756321914694</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -28939,28 +29030,28 @@
         <v>0.1224</v>
       </c>
       <c r="I19" t="n">
-        <v>0.182316188465841</v>
+        <v>0.1776666252419404</v>
       </c>
       <c r="J19" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K19" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L19" t="n">
-        <v>0.03712302673284751</v>
+        <v>0.03544890509279774</v>
       </c>
       <c r="M19" t="n">
-        <v>5.672540885411515</v>
+        <v>5.671414895771879</v>
       </c>
       <c r="N19" t="n">
-        <v>45.54908161912865</v>
+        <v>45.55277433319127</v>
       </c>
       <c r="O19" t="n">
-        <v>6.749005972669505</v>
+        <v>6.749279541787499</v>
       </c>
       <c r="P19" t="n">
-        <v>360.5317671589279</v>
+        <v>360.5849111445556</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -29017,28 +29108,28 @@
         <v>0.1034</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1956039691030688</v>
+        <v>0.1925158773390898</v>
       </c>
       <c r="J20" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K20" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L20" t="n">
-        <v>0.04573367499194025</v>
+        <v>0.04460253052681895</v>
       </c>
       <c r="M20" t="n">
-        <v>5.458456675389725</v>
+        <v>5.450771704279455</v>
       </c>
       <c r="N20" t="n">
-        <v>42.17844454536977</v>
+        <v>42.1054590653094</v>
       </c>
       <c r="O20" t="n">
-        <v>6.494493401749653</v>
+        <v>6.48887194089307</v>
       </c>
       <c r="P20" t="n">
-        <v>365.9563132752721</v>
+        <v>365.9916098174243</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -29095,28 +29186,28 @@
         <v>0.0847</v>
       </c>
       <c r="I21" t="n">
-        <v>0.08704303084681728</v>
+        <v>0.08375993769814102</v>
       </c>
       <c r="J21" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K21" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L21" t="n">
-        <v>0.008172613004906126</v>
+        <v>0.007614726682007689</v>
       </c>
       <c r="M21" t="n">
-        <v>5.767664840262339</v>
+        <v>5.757885370014102</v>
       </c>
       <c r="N21" t="n">
-        <v>48.57859029604669</v>
+        <v>48.49303836402972</v>
       </c>
       <c r="O21" t="n">
-        <v>6.969834309081292</v>
+        <v>6.963694304320784</v>
       </c>
       <c r="P21" t="n">
-        <v>378.1908374501887</v>
+        <v>378.2283628362745</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -29173,28 +29264,28 @@
         <v>0.0767</v>
       </c>
       <c r="I22" t="n">
-        <v>0.01463744995256118</v>
+        <v>0.01186243741041271</v>
       </c>
       <c r="J22" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K22" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0002754233636386161</v>
+        <v>0.0001819751872923492</v>
       </c>
       <c r="M22" t="n">
-        <v>5.290021859050445</v>
+        <v>5.282114443217885</v>
       </c>
       <c r="N22" t="n">
-        <v>41.08773241167998</v>
+        <v>41.00505213791488</v>
       </c>
       <c r="O22" t="n">
-        <v>6.409971326899987</v>
+        <v>6.403518730972439</v>
       </c>
       <c r="P22" t="n">
-        <v>384.6918610882262</v>
+        <v>384.7235791700233</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -29251,28 +29342,28 @@
         <v>0.0697</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.04016641579910391</v>
+        <v>-0.04427635207340995</v>
       </c>
       <c r="J23" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K23" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L23" t="n">
-        <v>0.002186715958077956</v>
+        <v>0.002666688845905374</v>
       </c>
       <c r="M23" t="n">
-        <v>5.189557052758834</v>
+        <v>5.19073486750421</v>
       </c>
       <c r="N23" t="n">
-        <v>38.89419641984455</v>
+        <v>38.88591820517433</v>
       </c>
       <c r="O23" t="n">
-        <v>6.236521179298965</v>
+        <v>6.235857455488727</v>
       </c>
       <c r="P23" t="n">
-        <v>378.8401034927127</v>
+        <v>378.8870796028921</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -29329,28 +29420,28 @@
         <v>0.06610000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1259334661564122</v>
+        <v>-0.1327355517567872</v>
       </c>
       <c r="J24" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K24" t="n">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="L24" t="n">
-        <v>0.01430580578485185</v>
+        <v>0.01588973367642454</v>
       </c>
       <c r="M24" t="n">
-        <v>6.263421825832775</v>
+        <v>6.27226223123784</v>
       </c>
       <c r="N24" t="n">
-        <v>57.73164389607857</v>
+        <v>57.87385031076383</v>
       </c>
       <c r="O24" t="n">
-        <v>7.598134237829611</v>
+        <v>7.607486464711181</v>
       </c>
       <c r="P24" t="n">
-        <v>386.5943283601321</v>
+        <v>386.672075434852</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -29388,7 +29479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y296"/>
+  <dimension ref="A1:Y297"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66899,6 +66990,133 @@
         </is>
       </c>
     </row>
+    <row r="297">
+      <c r="A297" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>-36.26035493395069,175.4897885598137</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>-36.261077445727196,175.4899676356457</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>-36.261748892486914,175.49030422240892</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>-36.26239649415403,175.49071435047796</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>-36.26304805653685,175.49111492728062</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>-36.263661560045335,175.491564318882</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>-36.264237743855105,175.4921167205381</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>-36.26480415064117,175.49268161785173</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>-36.265281824165314,175.49336172136438</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>-36.265524907202824,175.49434640772384</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>-36.26631791520142,175.49461571088102</t>
+        </is>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>-36.26676633737254,175.49530999354343</t>
+        </is>
+      </c>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>-36.26717055540531,175.4960559447716</t>
+        </is>
+      </c>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>-36.267538635712164,175.49682950473922</t>
+        </is>
+      </c>
+      <c r="P297" t="inlineStr">
+        <is>
+          <t>-36.26787241158317,175.49762482421878</t>
+        </is>
+      </c>
+      <c r="Q297" t="inlineStr">
+        <is>
+          <t>-36.26819058606926,175.49840615205176</t>
+        </is>
+      </c>
+      <c r="R297" t="inlineStr">
+        <is>
+          <t>-36.268420619341434,175.49925048399203</t>
+        </is>
+      </c>
+      <c r="S297" t="inlineStr">
+        <is>
+          <t>-36.268642446022966,175.5001083108256</t>
+        </is>
+      </c>
+      <c r="T297" t="inlineStr">
+        <is>
+          <t>-36.2687510363304,175.5009994690475</t>
+        </is>
+      </c>
+      <c r="U297" t="inlineStr">
+        <is>
+          <t>-36.2688506145406,175.50188618799365</t>
+        </is>
+      </c>
+      <c r="V297" t="inlineStr">
+        <is>
+          <t>-36.2689203417765,175.50273954100405</t>
+        </is>
+      </c>
+      <c r="W297" t="inlineStr">
+        <is>
+          <t>-36.2689592518627,175.5036187965339</t>
+        </is>
+      </c>
+      <c r="X297" t="inlineStr">
+        <is>
+          <t>-36.268900006049044,175.5045139740116</t>
+        </is>
+      </c>
+      <c r="Y297" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0122/nzd0122.xlsx
+++ b/data/nzd0122/nzd0122.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y297"/>
+  <dimension ref="A1:Y298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24492,6 +24492,87 @@
         </is>
       </c>
     </row>
+    <row r="298">
+      <c r="A298" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:05:36+00:00</t>
+        </is>
+      </c>
+      <c r="B298" t="n">
+        <v>355.69</v>
+      </c>
+      <c r="C298" t="n">
+        <v>344.57</v>
+      </c>
+      <c r="D298" t="n">
+        <v>345.03</v>
+      </c>
+      <c r="E298" t="n">
+        <v>351.98</v>
+      </c>
+      <c r="F298" t="n">
+        <v>360.84</v>
+      </c>
+      <c r="G298" t="n">
+        <v>361.43</v>
+      </c>
+      <c r="H298" t="n">
+        <v>353.05</v>
+      </c>
+      <c r="I298" t="n">
+        <v>349.13</v>
+      </c>
+      <c r="J298" t="n">
+        <v>356.75</v>
+      </c>
+      <c r="K298" t="n">
+        <v>405.95</v>
+      </c>
+      <c r="L298" t="n">
+        <v>361.52</v>
+      </c>
+      <c r="M298" t="n">
+        <v>363.29</v>
+      </c>
+      <c r="N298" t="n">
+        <v>359.36</v>
+      </c>
+      <c r="O298" t="n">
+        <v>360.93</v>
+      </c>
+      <c r="P298" t="n">
+        <v>366.83</v>
+      </c>
+      <c r="Q298" t="n">
+        <v>367.58</v>
+      </c>
+      <c r="R298" t="n">
+        <v>362.82</v>
+      </c>
+      <c r="S298" t="n">
+        <v>356.12</v>
+      </c>
+      <c r="T298" t="n">
+        <v>364.85</v>
+      </c>
+      <c r="U298" t="n">
+        <v>373.67</v>
+      </c>
+      <c r="V298" t="n">
+        <v>380.68</v>
+      </c>
+      <c r="W298" t="n">
+        <v>371.88</v>
+      </c>
+      <c r="X298" t="n">
+        <v>371.33</v>
+      </c>
+      <c r="Y298" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -24503,7 +24584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B303"/>
+  <dimension ref="A1:B304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27536,6 +27617,16 @@
       </c>
       <c r="B303" t="n">
         <v>0.32</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B304" t="n">
+        <v>0.84</v>
       </c>
     </row>
   </sheetData>
@@ -27704,28 +27795,28 @@
         <v>0.1526</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2012791172244049</v>
+        <v>0.1992532011816733</v>
       </c>
       <c r="J2" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K2" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05761573033569178</v>
+        <v>0.05687419785923897</v>
       </c>
       <c r="M2" t="n">
-        <v>4.597467509547885</v>
+        <v>4.589882875599548</v>
       </c>
       <c r="N2" t="n">
-        <v>34.66256537174345</v>
+        <v>34.57432797709494</v>
       </c>
       <c r="O2" t="n">
-        <v>5.887492282096296</v>
+        <v>5.879993875600122</v>
       </c>
       <c r="P2" t="n">
-        <v>353.1772930330886</v>
+        <v>353.2007770214207</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -27782,28 +27873,28 @@
         <v>0.1234</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1301103447817787</v>
+        <v>0.127806412223985</v>
       </c>
       <c r="J3" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K3" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02646622213420124</v>
+        <v>0.02571518498167524</v>
       </c>
       <c r="M3" t="n">
-        <v>4.793657782180372</v>
+        <v>4.786763116536659</v>
       </c>
       <c r="N3" t="n">
-        <v>32.57309555709423</v>
+        <v>32.500523668002</v>
       </c>
       <c r="O3" t="n">
-        <v>5.707284429314369</v>
+        <v>5.700923054032741</v>
       </c>
       <c r="P3" t="n">
-        <v>344.3989009846618</v>
+        <v>344.4256076813679</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -27860,28 +27951,28 @@
         <v>0.1286</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09282484298846298</v>
+        <v>0.09073097506286071</v>
       </c>
       <c r="J4" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K4" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00836745263991201</v>
+        <v>0.008050943816930056</v>
       </c>
       <c r="M4" t="n">
-        <v>5.998407572566356</v>
+        <v>5.986235478018234</v>
       </c>
       <c r="N4" t="n">
-        <v>53.4148807475086</v>
+        <v>53.26507213059021</v>
       </c>
       <c r="O4" t="n">
-        <v>7.308548470627297</v>
+        <v>7.298292411968036</v>
       </c>
       <c r="P4" t="n">
-        <v>345.5586000315088</v>
+        <v>345.5828717036298</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -27938,28 +28029,28 @@
         <v>0.1132</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1010523720412122</v>
+        <v>0.09841925493744645</v>
       </c>
       <c r="J5" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K5" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L5" t="n">
-        <v>0.009146703926998567</v>
+        <v>0.008736282179021893</v>
       </c>
       <c r="M5" t="n">
-        <v>6.161806085336472</v>
+        <v>6.15108255458531</v>
       </c>
       <c r="N5" t="n">
-        <v>57.864748291048</v>
+        <v>57.71802923455038</v>
       </c>
       <c r="O5" t="n">
-        <v>7.606888213392385</v>
+        <v>7.597238263642281</v>
       </c>
       <c r="P5" t="n">
-        <v>353.0758525814548</v>
+        <v>353.1063751154777</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -28016,28 +28107,28 @@
         <v>0.1246</v>
       </c>
       <c r="I6" t="n">
-        <v>0.115446125831547</v>
+        <v>0.1120581516057831</v>
       </c>
       <c r="J6" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K6" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01084974921391113</v>
+        <v>0.01029010877854752</v>
       </c>
       <c r="M6" t="n">
-        <v>6.379454916693716</v>
+        <v>6.371370879922159</v>
       </c>
       <c r="N6" t="n">
-        <v>63.55907952135894</v>
+        <v>63.42546274695946</v>
       </c>
       <c r="O6" t="n">
-        <v>7.972394842289169</v>
+        <v>7.964010468787661</v>
       </c>
       <c r="P6" t="n">
-        <v>362.6400053359256</v>
+        <v>362.6792780133266</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -28094,28 +28185,28 @@
         <v>0.1069</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1054524199561186</v>
+        <v>0.1008971772626729</v>
       </c>
       <c r="J7" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K7" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01074123938623472</v>
+        <v>0.009886889176183744</v>
       </c>
       <c r="M7" t="n">
-        <v>5.812891013406333</v>
+        <v>5.812878817195753</v>
       </c>
       <c r="N7" t="n">
-        <v>53.57287050242482</v>
+        <v>53.53921123671705</v>
       </c>
       <c r="O7" t="n">
-        <v>7.319349049090692</v>
+        <v>7.317049353169422</v>
       </c>
       <c r="P7" t="n">
-        <v>365.2089448866692</v>
+        <v>365.2617482921444</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -28172,28 +28263,28 @@
         <v>0.1028</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1234420504843355</v>
+        <v>0.1202718293215858</v>
       </c>
       <c r="J8" t="n">
+        <v>297</v>
+      </c>
+      <c r="K8" t="n">
         <v>296</v>
       </c>
-      <c r="K8" t="n">
-        <v>295</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.01525703621230035</v>
+        <v>0.01457993910058053</v>
       </c>
       <c r="M8" t="n">
-        <v>5.937912320047518</v>
+        <v>5.930434628317866</v>
       </c>
       <c r="N8" t="n">
-        <v>51.43769217879193</v>
+        <v>51.33547049986243</v>
       </c>
       <c r="O8" t="n">
-        <v>7.17200754174115</v>
+        <v>7.16487756349419</v>
       </c>
       <c r="P8" t="n">
-        <v>354.3232105555913</v>
+        <v>354.3599206857106</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -28250,28 +28341,28 @@
         <v>0.103</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1207391676244684</v>
+        <v>0.1182162801599869</v>
       </c>
       <c r="J9" t="n">
+        <v>297</v>
+      </c>
+      <c r="K9" t="n">
         <v>296</v>
       </c>
-      <c r="K9" t="n">
-        <v>295</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.01310513887191045</v>
+        <v>0.01265163870141151</v>
       </c>
       <c r="M9" t="n">
-        <v>6.202461749368298</v>
+        <v>6.191539255392484</v>
       </c>
       <c r="N9" t="n">
-        <v>57.41536455289468</v>
+        <v>57.26670981592643</v>
       </c>
       <c r="O9" t="n">
-        <v>7.577292692835264</v>
+        <v>7.567477110366864</v>
       </c>
       <c r="P9" t="n">
-        <v>349.5296125176093</v>
+        <v>349.5588267340133</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -28328,28 +28419,28 @@
         <v>0.1145</v>
       </c>
       <c r="I10" t="n">
-        <v>0.03719326192148134</v>
+        <v>0.03666302755098318</v>
       </c>
       <c r="J10" t="n">
+        <v>297</v>
+      </c>
+      <c r="K10" t="n">
         <v>296</v>
       </c>
-      <c r="K10" t="n">
-        <v>295</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.00156287624424345</v>
+        <v>0.001529816776563719</v>
       </c>
       <c r="M10" t="n">
-        <v>5.316072485564702</v>
+        <v>5.300662265652401</v>
       </c>
       <c r="N10" t="n">
-        <v>46.21970605044874</v>
+        <v>46.06556006458224</v>
       </c>
       <c r="O10" t="n">
-        <v>6.798507634065636</v>
+        <v>6.787161414360368</v>
       </c>
       <c r="P10" t="n">
-        <v>356.5137283805143</v>
+        <v>356.5198683220942</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -28406,28 +28497,28 @@
         <v>0.0873</v>
       </c>
       <c r="I11" t="n">
-        <v>0.306272501298106</v>
+        <v>0.3024942766547319</v>
       </c>
       <c r="J11" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K11" t="n">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="L11" t="n">
-        <v>0.05727699849830825</v>
+        <v>0.05627279637749405</v>
       </c>
       <c r="M11" t="n">
-        <v>7.082993746485276</v>
+        <v>7.078225006898212</v>
       </c>
       <c r="N11" t="n">
-        <v>80.8265484277688</v>
+        <v>80.65444201657361</v>
       </c>
       <c r="O11" t="n">
-        <v>8.990358637327478</v>
+        <v>8.980781815441995</v>
       </c>
       <c r="P11" t="n">
-        <v>403.1464127653821</v>
+        <v>403.1901871788654</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -28484,28 +28575,28 @@
         <v>0.1136</v>
       </c>
       <c r="I12" t="n">
-        <v>0.04896695358192362</v>
+        <v>0.04616401535810689</v>
       </c>
       <c r="J12" t="n">
+        <v>297</v>
+      </c>
+      <c r="K12" t="n">
         <v>296</v>
       </c>
-      <c r="K12" t="n">
-        <v>295</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.003600538139880483</v>
+        <v>0.003219761794414966</v>
       </c>
       <c r="M12" t="n">
-        <v>4.771563162132486</v>
+        <v>4.766267714584746</v>
       </c>
       <c r="N12" t="n">
-        <v>34.70361779917722</v>
+        <v>34.6423108568452</v>
       </c>
       <c r="O12" t="n">
-        <v>5.890977660726377</v>
+        <v>5.885771899831423</v>
       </c>
       <c r="P12" t="n">
-        <v>364.2797264408692</v>
+        <v>364.3121835539948</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -28562,28 +28653,28 @@
         <v>0.0838</v>
       </c>
       <c r="I13" t="n">
-        <v>0.06471301620223346</v>
+        <v>0.0618140468697092</v>
       </c>
       <c r="J13" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K13" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L13" t="n">
-        <v>0.004712617099758787</v>
+        <v>0.004327361516508477</v>
       </c>
       <c r="M13" t="n">
-        <v>5.751273081306058</v>
+        <v>5.742863915672197</v>
       </c>
       <c r="N13" t="n">
-        <v>46.90836998533674</v>
+        <v>46.81152852259241</v>
       </c>
       <c r="O13" t="n">
-        <v>6.848968534409889</v>
+        <v>6.841895097309839</v>
       </c>
       <c r="P13" t="n">
-        <v>365.8125805095665</v>
+        <v>365.8458628623986</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -28640,28 +28731,28 @@
         <v>0.0814</v>
       </c>
       <c r="I14" t="n">
-        <v>0.09508873101055224</v>
+        <v>0.09060524161760124</v>
       </c>
       <c r="J14" t="n">
+        <v>297</v>
+      </c>
+      <c r="K14" t="n">
         <v>296</v>
       </c>
-      <c r="K14" t="n">
-        <v>295</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.01035029062092463</v>
+        <v>0.009445222491701655</v>
       </c>
       <c r="M14" t="n">
-        <v>5.550141353935225</v>
+        <v>5.549792358657135</v>
       </c>
       <c r="N14" t="n">
-        <v>45.21573261476813</v>
+        <v>45.20609301484151</v>
       </c>
       <c r="O14" t="n">
-        <v>6.724264466450448</v>
+        <v>6.723547650968312</v>
       </c>
       <c r="P14" t="n">
-        <v>363.3244337747316</v>
+        <v>363.3763511238861</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -28718,28 +28809,28 @@
         <v>0.09660000000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.03836915247595857</v>
+        <v>0.03428480360313629</v>
       </c>
       <c r="J15" t="n">
+        <v>297</v>
+      </c>
+      <c r="K15" t="n">
         <v>296</v>
       </c>
-      <c r="K15" t="n">
-        <v>295</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.001704314248293648</v>
+        <v>0.001367666385104105</v>
       </c>
       <c r="M15" t="n">
-        <v>5.60963651216357</v>
+        <v>5.605914268382357</v>
       </c>
       <c r="N15" t="n">
-        <v>45.09998979891246</v>
+        <v>45.06639375735111</v>
       </c>
       <c r="O15" t="n">
-        <v>6.715652596651532</v>
+        <v>6.713150806987067</v>
       </c>
       <c r="P15" t="n">
-        <v>365.8512505975793</v>
+        <v>365.8985460293099</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -28796,28 +28887,28 @@
         <v>0.0959</v>
       </c>
       <c r="I16" t="n">
-        <v>0.113272714540509</v>
+        <v>0.1084479628317129</v>
       </c>
       <c r="J16" t="n">
+        <v>297</v>
+      </c>
+      <c r="K16" t="n">
         <v>296</v>
       </c>
-      <c r="K16" t="n">
-        <v>295</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.01342310498478394</v>
+        <v>0.01236629217043717</v>
       </c>
       <c r="M16" t="n">
-        <v>5.927478526576269</v>
+        <v>5.926690862903021</v>
       </c>
       <c r="N16" t="n">
-        <v>49.32091007821322</v>
+        <v>49.32001747029358</v>
       </c>
       <c r="O16" t="n">
-        <v>7.022884740490421</v>
+        <v>7.022821190254923</v>
       </c>
       <c r="P16" t="n">
-        <v>370.7986392109418</v>
+        <v>370.8545082667363</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -28874,28 +28965,28 @@
         <v>0.0883</v>
       </c>
       <c r="I17" t="n">
-        <v>0.214055878418695</v>
+        <v>0.2064766075647768</v>
       </c>
       <c r="J17" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K17" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L17" t="n">
-        <v>0.04579875039821402</v>
+        <v>0.0427104188792462</v>
       </c>
       <c r="M17" t="n">
-        <v>5.974562904177546</v>
+        <v>5.985043765633146</v>
       </c>
       <c r="N17" t="n">
-        <v>50.63156877271932</v>
+        <v>50.87873296160723</v>
       </c>
       <c r="O17" t="n">
-        <v>7.115586326699952</v>
+        <v>7.132932984516763</v>
       </c>
       <c r="P17" t="n">
-        <v>372.9672235225914</v>
+        <v>373.054239264338</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -28952,28 +29043,28 @@
         <v>0.0919</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1786253453655476</v>
+        <v>0.1742910894803058</v>
       </c>
       <c r="J18" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K18" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L18" t="n">
-        <v>0.03455048276633432</v>
+        <v>0.03308929063478616</v>
       </c>
       <c r="M18" t="n">
-        <v>5.793461454326768</v>
+        <v>5.791418107136388</v>
       </c>
       <c r="N18" t="n">
-        <v>47.28706140509722</v>
+        <v>47.26442259815919</v>
       </c>
       <c r="O18" t="n">
-        <v>6.876558834555058</v>
+        <v>6.87491255203724</v>
       </c>
       <c r="P18" t="n">
-        <v>364.3756321914694</v>
+        <v>364.4253927156732</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -29030,28 +29121,28 @@
         <v>0.1224</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1776666252419404</v>
+        <v>0.1713779679070281</v>
       </c>
       <c r="J19" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K19" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L19" t="n">
-        <v>0.03544890509279774</v>
+        <v>0.03309681529714592</v>
       </c>
       <c r="M19" t="n">
-        <v>5.671414895771879</v>
+        <v>5.676353922261151</v>
       </c>
       <c r="N19" t="n">
-        <v>45.55277433319127</v>
+        <v>45.68691528743367</v>
       </c>
       <c r="O19" t="n">
-        <v>6.749279541787499</v>
+        <v>6.75920966440853</v>
       </c>
       <c r="P19" t="n">
-        <v>360.5849111445556</v>
+        <v>360.6571096703947</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -29108,28 +29199,28 @@
         <v>0.1034</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1925158773390898</v>
+        <v>0.1882037988811478</v>
       </c>
       <c r="J20" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K20" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L20" t="n">
-        <v>0.04460253052681895</v>
+        <v>0.04287839287249484</v>
       </c>
       <c r="M20" t="n">
-        <v>5.450771704279455</v>
+        <v>5.44740584878625</v>
       </c>
       <c r="N20" t="n">
-        <v>42.1054590653094</v>
+        <v>42.09887263930624</v>
       </c>
       <c r="O20" t="n">
-        <v>6.48887194089307</v>
+        <v>6.488364404016335</v>
       </c>
       <c r="P20" t="n">
-        <v>365.9916098174243</v>
+        <v>366.0411157280481</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -29186,28 +29277,28 @@
         <v>0.0847</v>
       </c>
       <c r="I21" t="n">
-        <v>0.08375993769814102</v>
+        <v>0.07913595541902504</v>
       </c>
       <c r="J21" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K21" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L21" t="n">
-        <v>0.007614726682007689</v>
+        <v>0.006830412293702293</v>
       </c>
       <c r="M21" t="n">
-        <v>5.757885370014102</v>
+        <v>5.752079955431311</v>
       </c>
       <c r="N21" t="n">
-        <v>48.49303836402972</v>
+        <v>48.485208458687</v>
       </c>
       <c r="O21" t="n">
-        <v>6.963694304320784</v>
+        <v>6.963132086833267</v>
       </c>
       <c r="P21" t="n">
-        <v>378.2283628362745</v>
+        <v>378.281449637841</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -29264,28 +29355,28 @@
         <v>0.0767</v>
       </c>
       <c r="I22" t="n">
-        <v>0.01186243741041271</v>
+        <v>0.008904957507325289</v>
       </c>
       <c r="J22" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K22" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0001819751872923492</v>
+        <v>0.000103146880110927</v>
       </c>
       <c r="M22" t="n">
-        <v>5.282114443217885</v>
+        <v>5.274970292374649</v>
       </c>
       <c r="N22" t="n">
-        <v>41.00505213791488</v>
+        <v>40.93057841349913</v>
       </c>
       <c r="O22" t="n">
-        <v>6.403518730972439</v>
+        <v>6.397701025641878</v>
       </c>
       <c r="P22" t="n">
-        <v>384.7235791700233</v>
+        <v>384.7575332683037</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -29342,28 +29433,28 @@
         <v>0.0697</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.04427635207340995</v>
+        <v>-0.04820852198733468</v>
       </c>
       <c r="J23" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K23" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L23" t="n">
-        <v>0.002666688845905374</v>
+        <v>0.003173705974948815</v>
       </c>
       <c r="M23" t="n">
-        <v>5.19073486750421</v>
+        <v>5.190910992746692</v>
       </c>
       <c r="N23" t="n">
-        <v>38.88591820517433</v>
+        <v>38.86740118634777</v>
       </c>
       <c r="O23" t="n">
-        <v>6.235857455488727</v>
+        <v>6.234372557551223</v>
       </c>
       <c r="P23" t="n">
-        <v>378.8870796028921</v>
+        <v>378.9322238771011</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -29420,28 +29511,28 @@
         <v>0.06610000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1327355517567872</v>
+        <v>-0.1406825044872061</v>
       </c>
       <c r="J24" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K24" t="n">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="L24" t="n">
-        <v>0.01588973367642454</v>
+        <v>0.01780338588716712</v>
       </c>
       <c r="M24" t="n">
-        <v>6.27226223123784</v>
+        <v>6.286472314780953</v>
       </c>
       <c r="N24" t="n">
-        <v>57.87385031076383</v>
+        <v>58.13813335234975</v>
       </c>
       <c r="O24" t="n">
-        <v>7.607486464711181</v>
+        <v>7.624836611518292</v>
       </c>
       <c r="P24" t="n">
-        <v>386.672075434852</v>
+        <v>386.7633124416554</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -29479,7 +29570,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y297"/>
+  <dimension ref="A1:Y298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67117,6 +67208,133 @@
         </is>
       </c>
     </row>
+    <row r="298">
+      <c r="A298" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:05:36+00:00</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>-36.260355067876425,175.48978814667117</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>-36.26106904186388,175.489993560561</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>-36.261744238525765,175.49031857934068</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>-36.26239769950606,175.4907106321107</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>-36.263045141351526,175.49112220766452</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>-36.26365926798241,175.4915680370068</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>-36.26424401512628,175.4921085779279</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>-36.26480110813165,175.4926855682392</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>-36.26528654318263,175.4933555942264</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>-36.26551379258566,175.49436083867036</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>-36.26632233915605,175.49461080390213</t>
+        </is>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>-36.266754285425804,175.4953201613638</t>
+        </is>
+      </c>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>-36.267170478435794,175.49605600260833</t>
+        </is>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>-36.267544793290824,175.49682487782144</t>
+        </is>
+      </c>
+      <c r="P298" t="inlineStr">
+        <is>
+          <t>-36.26788479185144,175.4976163738241</t>
+        </is>
+      </c>
+      <c r="Q298" t="inlineStr">
+        <is>
+          <t>-36.268206171264076,175.4983991728257</t>
+        </is>
+      </c>
+      <c r="R298" t="inlineStr">
+        <is>
+          <t>-36.268425965614995,175.49924891025134</t>
+        </is>
+      </c>
+      <c r="S298" t="inlineStr">
+        <is>
+          <t>-36.26866418171264,175.50010191280683</t>
+        </is>
+      </c>
+      <c r="T298" t="inlineStr">
+        <is>
+          <t>-36.26876716282594,175.50099472224795</t>
+        </is>
+      </c>
+      <c r="U298" t="inlineStr">
+        <is>
+          <t>-36.26886856852503,175.50188187746073</t>
+        </is>
+      </c>
+      <c r="V298" t="inlineStr">
+        <is>
+          <t>-36.26892313324618,175.50273942401643</t>
+        </is>
+      </c>
+      <c r="W298" t="inlineStr">
+        <is>
+          <t>-36.26895745573981,175.50361861719827</t>
+        </is>
+      </c>
+      <c r="X298" t="inlineStr">
+        <is>
+          <t>-36.26891626094613,175.50451559711797</t>
+        </is>
+      </c>
+      <c r="Y298" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
